--- a/artfynd/Käringberget SO artfynd.xlsx
+++ b/artfynd/Käringberget SO artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1931007</v>
+        <v>444017</v>
       </c>
       <c r="B2" t="n">
-        <v>80118</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677656</v>
+        <v>677873</v>
       </c>
       <c r="R2" t="n">
-        <v>7111309</v>
+        <v>7111158</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-08-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>444017</v>
+        <v>1890449</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677873</v>
+        <v>677656</v>
       </c>
       <c r="R3" t="n">
-        <v>7111158</v>
+        <v>7111309</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-08-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>2052096</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1998234</v>
+        <v>1931007</v>
       </c>
       <c r="B5" t="n">
-        <v>80119</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>70231196</v>
+        <v>1998234</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678334</v>
+        <v>677656</v>
       </c>
       <c r="R6" t="n">
-        <v>7111104</v>
+        <v>7111309</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-03-29</t>
+          <t>2007-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-03-29</t>
+          <t>2007-08-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1153,12 +1153,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
         <v>65143014</v>
       </c>
       <c r="B7" t="n">
-        <v>39422</v>
+        <v>39652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1890449</v>
+        <v>70231196</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677656</v>
+        <v>678334</v>
       </c>
       <c r="R8" t="n">
-        <v>7111309</v>
+        <v>7111104</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2007-08-26</t>
+          <t>2018-03-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2007-08-26</t>
+          <t>2018-03-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1356,12 +1356,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
